--- a/extenbooks/S403_extenbook.xlsx
+++ b/extenbooks/S403_extenbook.xlsx
@@ -1951,7 +1951,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -2779,11 +2779,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2806,76 +2806,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Profit derivation from S401 (tc') + S402 (tc) at output price p=7 (Fig 4.18).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S403_research.json", "adequacy_report": "Technical/docs/chapters/CH4_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S403_DPR.md", "epr": "Technical/docs/series/S403_EPR.md", "loader": "Technical/code/L01_loaders/L01_S403_load.py", "processor": "Technical/code/P02_processors/P02_S403_construct.py", "validator": "Technical/code/V03_validators/V03_S403_validate.py", "processed": "Technical/data/processed/S403.parquet", "chopped_csv": "Technical/chopped/S403.csv", "extenbook_xlsx": "Technical/extenbooks/S403_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>updated_at</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-18T21:57:52.480731+00:00</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S403_extenbook.xlsx
+++ b/extenbooks/S403_extenbook.xlsx
@@ -1930,14 +1930,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>**Data Provenance Record (DPR)**</t>
+          <t>**Data Provenance Record (DPR)** — the internal, full-provenance companion to the public Explainer.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Phase**: 5 (Ingestion)</t>
+          <t>**Record type**: Data Provenance Record (source-and-construction detail)</t>
         </is>
       </c>
     </row>
@@ -1965,7 +1965,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-ch4-fanout</t>
+          <t>**Prepared by**: RSCD data-construction pipeline</t>
         </is>
       </c>
     </row>
@@ -1979,7 +1979,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>- Research dossier: `Technical/research/S403_research.json`</t>
+          <t>- Series research notes: `Technical/research/S403_research.json`</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>| **S403-A** | XR rows 0–20 (21 points) | Shaikh, *Capitalism* (2016), Appendix 4.2 Table 4.2.4, profit columns | money units | Reconstructed CSV `SalvagedInputs/book_data/Reconstructed/Appendix_4_2_Table4.csv`, columns `XR`, `PL`, `PH` |</t>
+          <t>| **S403-A** (the dataset's two profit columns) | output rows 0–20 (21 points) | Shaikh, *Capitalism* (2016), Appendix 4.2 Table 4.2.4, profit columns | money units | Reconstructed CSV `SalvagedInputs/book_data/Reconstructed/Appendix_4_2_Table4.csv`, columns `XR`, `PL`, `PH` |</t>
         </is>
       </c>
     </row>
@@ -2138,7 +2138,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>`derived` / `formula`. Loader consumes the tabulated profit columns from the same CSV as S401/S402.</t>
+          <t>A `derived` series (built by formula). The data-loading step reads the tabulated profit columns from the same table as S401/S402.</t>
         </is>
       </c>
     </row>
@@ -2293,7 +2293,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>- **Cross-series**: derives from S401 (tc') and S402 (tc). Cross_references field in registry records this dependency.</t>
+          <t>- **Cross-series**: derives from S401 (per-worker total cost) and S402 (per-hour total cost); the registry records this dependency.</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2320,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>- **Expected MAE**: 0 — direct CSV round-trip.</t>
+          <t>- **Expected mean absolute error (MAE)**: 0 — a direct round-trip of the same table (via the validation step).</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>**Phase**: 6 (Extension)</t>
+          <t>**Record type**: Extension Provenance Record</t>
         </is>
       </c>
     </row>
@@ -2378,7 +2378,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-ch4-fanout</t>
+          <t>**Author**: RSCD data-construction pipeline</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Same as S401_EPR / S402_EPR for `derived` content type. No extension attempted; no proxy; no synthetic data; no CD2 divergence (no CD2 predecessor).</t>
+          <t>Same as S401_EPR / S402_EPR for `derived` content type. No extension attempted; no proxy; no synthetic data; no predecessor divergence (this series has no predecessor — it was first constructed in this dataset).</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-18T21:59:45.753660+00:00</t>
+          <t>2026-07-02T06:22:48.912472+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S403_extenbook.xlsx
+++ b/extenbooks/S403_extenbook.xlsx
@@ -2764,7 +2764,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-02T06:22:48.912472+00:00</t>
+          <t>2026-07-11T03:44:24.844453+00:00</t>
         </is>
       </c>
     </row>
@@ -2779,11 +2779,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2806,6 +2806,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_APPENDIX_4_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Renderable two-trace profit curve (Shaikh Fig 4.18): total profit vs cumulative daily output XR, one trace for per-worker wages (PL = p*XR - tc') and one for per-hour wages (PH = p*XR - tc), at output price p=7. 2 subseries x 21 points = 42 rows, all non-null. Renders as overlaid x-y profit curves (x = cumulative output XR, 'year' index column 0-9, NOT calendar years). TRIAGE_PRESCREEN EMPTY flag is STALE: L01_S403/P02_S403 exist and replicate.py --series S403 builds the chopped (PASS, 42 rows). Derived from S401+S402, both verbatim from Appendix Table 4.2.4. KB note: the p.781 appendix passage AND Appendix Table 4.2.4 are present verbatim in ch18_appendices.md, so a KB-anchored 'From the book' quote is included.", "date": "2026-06-10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S403_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S403_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Profit derivation from S401 (tc') + S402 (tc) at output price p=7 (Fig 4.18).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>theoretical</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>money_units_illustrative</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
